--- a/Data Mapping.xlsx
+++ b/Data Mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Python_Data_Project\spotify_recommendation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5FACC0-FBF8-4527-9B3E-D518B04AC16F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF5CC98-2663-433A-8B3D-299B1E5C0A67}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8761A691-B5B4-402B-BE1C-9D3A0AFDB81D}"/>
   </bookViews>
